--- a/Tagihan/2026/Agustus/SMAN 2 Tanjung.xlsx
+++ b/Tagihan/2026/Agustus/SMAN 2 Tanjung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BB0F0D-AFC2-4615-83E7-2CF7585DEB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71365D6-7078-4CCF-BD52-E43A1DA5C0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="705" windowWidth="10845" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Perbaikan" sheetId="1" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>Unit</t>
   </si>
   <si>
-    <t>Lot</t>
-  </si>
-  <si>
     <r>
       <t>Tanjung,</t>
     </r>
@@ -102,10 +99,13 @@
     <t>Pasang Kipas Angin Baling Baling</t>
   </si>
   <si>
-    <t xml:space="preserve">Biaya Instalasi </t>
-  </si>
-  <si>
     <t>Kepada Tuan/Nyonya   SMAN 2 Tanjung</t>
+  </si>
+  <si>
+    <t>Clam No. 08</t>
+  </si>
+  <si>
+    <t>Pak</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1045,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" s="47"/>
     </row>
@@ -1055,7 +1055,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G14" s="48"/>
     </row>
@@ -1088,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="25">
         <v>22</v>
@@ -1100,7 +1100,7 @@
         <v>50000</v>
       </c>
       <c r="G17" s="15">
-        <f t="shared" ref="G17:G21" si="0">F17*D17</f>
+        <f t="shared" ref="G17:G18" si="0">F17*D17</f>
         <v>1100000</v>
       </c>
     </row>
@@ -1112,17 +1112,17 @@
         <v>19</v>
       </c>
       <c r="D18" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>100000</v>
+        <v>15000</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>2200000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="19" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1207,7 +1207,7 @@
       <c r="F28" s="44"/>
       <c r="G28" s="18">
         <f>SUM(G17:G27)</f>
-        <v>3300000</v>
+        <v>1130000</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
